--- a/fhir/ValueSet-phmr-observation-vs.xlsx
+++ b/fhir/ValueSet-phmr-observation-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -106,57 +106,30 @@
     <t>NPU03804</t>
   </si>
   <si>
-    <t>Pt—Legeme; masse = ? kg</t>
-  </si>
-  <si>
     <t>NPU19748</t>
   </si>
   <si>
-    <t>P—C-reaktivt protein; massek. = ? mg/L</t>
-  </si>
-  <si>
     <t>NPU22089</t>
   </si>
   <si>
-    <t>P(kB)—Glucose; stofk. = ? mmol/L</t>
-  </si>
-  <si>
     <t>NPU03963</t>
   </si>
   <si>
-    <t>U—Erythrocytter; arb.k.(proc.) = ?</t>
-  </si>
-  <si>
     <t>DNK05472</t>
   </si>
   <si>
-    <t>Blodtryk systolisk;Arm</t>
-  </si>
-  <si>
     <t>DNK05473</t>
   </si>
   <si>
-    <t>Blodtryk diastolisk;Arm</t>
-  </si>
-  <si>
     <t>NPU21692</t>
   </si>
   <si>
-    <t>Hjerte—Systole; frekv. = ? × 1/min</t>
-  </si>
-  <si>
     <t>NPU03011</t>
   </si>
   <si>
-    <t>Hb(Fe; O2-bind.; aB)—Oxygen(O2); mætn. = ?</t>
-  </si>
-  <si>
     <t>NPU27281</t>
   </si>
   <si>
-    <t>Pt—Legeme; massekoefficient(masse/kvadreret højde) = ? kg/m²</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -169,43 +142,25 @@
     <t>MCS88100</t>
   </si>
   <si>
-    <t>FEV6;Lunge</t>
-  </si>
-  <si>
     <t>MCS88015</t>
   </si>
   <si>
-    <t>FEV1;Lunge</t>
-  </si>
-  <si>
     <t>MCS88019</t>
   </si>
   <si>
-    <t>Blodtryk hjemme systolisk;Arm</t>
-  </si>
-  <si>
     <t>MCS88020</t>
   </si>
   <si>
-    <t>Blodtryk hjemme diastolisk;Arm</t>
-  </si>
-  <si>
     <t>MCS88050</t>
   </si>
   <si>
-    <t>Rejse sætte sig testen;Pt</t>
-  </si>
-  <si>
     <t>MCS88137</t>
   </si>
   <si>
-    <t>CAT score;Pt</t>
-  </si>
-  <si>
     <t>MCS88021</t>
   </si>
   <si>
-    <t>MRC skala;Pt(KOL)</t>
+    <t>MCS88214</t>
   </si>
   <si>
     <t>urn:oid:1.2.208.184.100.8</t>
@@ -491,88 +446,70 @@
       <c r="A2" t="s" s="2">
         <v>29</v>
       </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
-      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +519,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -599,74 +536,66 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>51</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="B2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>52</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>53</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>54</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>55</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>57</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>59</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>61</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>63</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>47</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>64</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/ValueSet-phmr-observation-vs.xlsx
+++ b/fhir/ValueSet-phmr-observation-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-phmr-observation-vs.xlsx
+++ b/fhir/ValueSet-phmr-observation-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-phmr-observation-vs.xlsx
+++ b/fhir/ValueSet-phmr-observation-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-phmr-observation-vs.xlsx
+++ b/fhir/ValueSet-phmr-observation-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-phmr-observation-vs.xlsx
+++ b/fhir/ValueSet-phmr-observation-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/ValueSet-phmr-observation-vs.xlsx
+++ b/fhir/ValueSet-phmr-observation-vs.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
